--- a/survey_templates/045_urban_planning_community_development_needs_assessment--survey_templates.xlsx
+++ b/survey_templates/045_urban_planning_community_development_needs_assessment--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="47" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,17 +515,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>resident_feedback</t>
+          <t>community_infrastructure</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Resident Feedback</t>
+          <t>Overall Condition of Community Infrastructure</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>priority_improvement_1</t>
+          <t>community_resources</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>What is the one thing that would have the most significant positive impact</t>
+          <t>Community Resources</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -566,12 +566,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>priority_improvement_2</t>
+          <t>public_services</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>What is the one thing that would have the most significant negative impact</t>
+          <t>Quality of Public Services</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -589,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>priority_improvement_3</t>
+          <t>priority_improvement_1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>What is the one thing that would have the most significant positive impact</t>
+          <t>First Priority Improvement</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -612,12 +612,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>priority_improvement_4</t>
+          <t>priority_improvement_2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>What is the one thing that would have the most significant positive impact</t>
+          <t>Second Priority Improvement</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>priority_improvement_5</t>
+          <t>priority_improvement_3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>What is the one thing that would have the most significant positive impact</t>
+          <t>Third Priority Improvement</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>priority_improvement_6</t>
+          <t>additional_feedback</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>What is the one thing that would have the most significant positive impact</t>
+          <t>Additional Feedback</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>priority_improvement_7</t>
+          <t>survey_submitter</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>What is the one thing that would have the most significant positive impact</t>
+          <t>How Did You Come Across This Survey?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>community_resource_1</t>
+          <t>contact_info</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>What community resources would be beneficial</t>
+          <t>Contact Info</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>community_resource_2</t>
+          <t>contact_email</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>What community resources would be beneficial</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>community_resource_3</t>
+          <t>contact_phone</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>What community resources would be beneficial</t>
+          <t>Phone</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,315 +773,16 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>community_resource_4</t>
+          <t>submit</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>What community resources would be beneficial</t>
+          <t>Submit</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>community_resource_5</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>What community resources would be beneficial</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>community_resource_6</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>What community resources would be beneficial</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>community_resource_7</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>What community resources would be beneficial</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>community_resource_8</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>What community resources would be beneficial</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>community_resource_9</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>What community resources would be beneficial</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>community_resource_10</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>What community resources would be beneficial</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>additional_feedback</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Do you have any other comments or feedback</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>survey_submitter</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>How did you come across this survey</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>contact_info</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Your contact info</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>survey_submitter_name</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Your Name</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>contact_email</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>contact_phone</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Phone</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>submit</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Submit</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +799,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="31" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,525 +827,270 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>resident_feedback_choices</t>
+          <t>priority_improvement_1_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>improve_road_conditions</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Improve Road Conditions</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>resident_feedback_choices</t>
+          <t>priority_improvement_1_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>enhance_public_transportation</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Enhance Public Transportation</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>priority_improvement_3_choices</t>
+          <t>priority_improvement_1_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>increase_access_to_parks</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Increase Access to Parks</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>priority_improvement_3_choices</t>
+          <t>priority_improvement_1_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>enhance_public_spaces</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>Enhance Public Spaces</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>priority_improvement_3_choices</t>
+          <t>priority_improvement_2_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>improve_public_healthcare</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Improve Public Healthcare</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>priority_improvement_3_choices</t>
+          <t>priority_improvement_2_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option_4</t>
+          <t>enhance_education_system</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Option 4</t>
+          <t>Enhance Education System</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>priority_improvement_3_choices</t>
+          <t>priority_improvement_2_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option_5</t>
+          <t>increase_public_safety</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Option 5</t>
+          <t>Increase Public Safety</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>priority_improvement_4_choices</t>
+          <t>priority_improvement_2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>support_community_events</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Support Community Events</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>priority_improvement_4_choices</t>
+          <t>priority_improvement_3_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>improve_public_transportation</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>Improve Public Transportation</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>priority_improvement_4_choices</t>
+          <t>priority_improvement_3_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>enhance_public_spaces</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Enhance Public Spaces</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>priority_improvement_4_choices</t>
+          <t>priority_improvement_3_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>option_4</t>
+          <t>increase_community_engagement</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Option 4</t>
+          <t>Increase Community Engagement</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>priority_improvement_4_choices</t>
+          <t>priority_improvement_3_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>option_5</t>
+          <t>support_local_businesses</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Option 5</t>
+          <t>Support Local Businesses</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>priority_improvement_5_choices</t>
+          <t>survey_submitter_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>website</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Website</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>priority_improvement_5_choices</t>
+          <t>survey_submitter_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>social_media</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>Social Media</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>priority_improvement_5_choices</t>
+          <t>survey_submitter_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>word_of_mouth</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Word of Mouth</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>priority_improvement_5_choices</t>
+          <t>survey_submitter_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>option_4</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
-        <is>
-          <t>Option 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>priority_improvement_5_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>option_5</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Option 5</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>priority_improvement_6_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>option_1</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Option 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>priority_improvement_6_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>option_2</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Option 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>priority_improvement_6_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>option_3</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Option 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>priority_improvement_6_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>option_4</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Option 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>priority_improvement_6_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>option_5</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Option 5</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>priority_improvement_7_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>option_1</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Option 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>priority_improvement_7_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>option_2</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Option 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>priority_improvement_7_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>option_3</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Option 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>priority_improvement_7_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>option_4</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Option 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>priority_improvement_7_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>option_5</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Option 5</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>survey_submitter_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>website</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Website</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>survey_submitter_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>social_media</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Social Media</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>survey_submitter_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>word_of_mouth</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Word of mouth</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>survey_submitter_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
